--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0070.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0070.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Hoàn thành "Chương Chính: Rạp Xiếc của Các Nhà Thông Thái" để mở khóa</t>
+          <t>Hoàn thành "Main Story: Circus of Savants" để mở khóa</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hoàn thành "Chương Phụ: Tổng Thống Hiện Tại" để mở khóa</t>
+          <t>Hoàn thành "Interlude: Current President" để mở khóa</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Mở Khóa Kết Thúc: "Thanh Bình"</t>
+          <t>Mở Kết Thúc: "Bình Yên"</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Mở Khóa Kết Thúc: "Hỗn Loạn"</t>
+          <t>Mở Kết Thúc: "Hỗn Loạn"</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Mở khóa Kết Thúc: "Bờ Biển Bị Che Khuất Trong Bí Ẩn"</t>
+          <t>Mở Kết Thúc: "Bờ Biển Bí Ẩn"</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mở Khóa Kết Thúc: "Người Canh Gác Vĩnh Hằng"</t>
+          <t>Mở Kết Thúc: "Người Canh Gác Vĩnh Hằng"</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Mở khóa Kết Thúc: "Những Linh Hồn Vượt Qua Hố Đen"</t>
+          <t>Mở Kết Thúc: "Linh Hồn Ngoài Hố Đen"</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Mở khóa Kết Thúc: "Đáy Biển Ngủ Yên" và "Cái Nôi Vĩnh Hằng"</t>
+          <t>Mở Kết Thúc: "Đáy Biển Ngủ Yên" và "Nôi Vĩnh Hằng"</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Mở khóa Kết Thúc: "Đáy Biển Ngủ Yên" và "Làn Gió Somnoire"</t>
+          <t>Mở khóa Kết thúc: "Vực Thẳm Ngủ Quên" và "Gió Ngủ Mơ"</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Verina đã tham gia đội của bạn</t>
+          <t>Verina đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Jiyan đã tham gia đội của bạn</t>
+          <t>Jiyan đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Zhezhi đã tham gia đội của bạn</t>
+          <t>Zhezhi đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Yuanwu đã tham gia đội của bạn</t>
+          <t>Yuanwu đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Yinlin đã tham gia đội của bạn</t>
+          <t>Yinlin đã gia nhập đội của cậu.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Lingyang đã tham gia đội của bạn</t>
+          <t>Lingyang đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Nhận 100 Mảnh Giấc mơ</t>
+          <t>Thu thập 100 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Bắt đầu trận chiến khó</t>
+          <t>Bắt đầu trận chiến khó khăn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Sau một khoảng lặng dài, một giọng nói thì thầm từ hư không:</t>
+          <t>Sau một khoảng lặng kéo dài, một giọng nói thì thầm từ hư không:</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Đúng như dự đoán, gương mặt quen thuộc đến phiền phức lại hiện lên màn hình…</t>
+          <t>Đúng như dự đoán, cái gương mặt đáng ghét quen thuộc lại hiện lên màn hình…</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>"The Psyche Meter"</t>
+          <t>"Đồng Hồ Tâm Thức"</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>"The Top Sentry"</t>
+          <t>"Lính Canh Tối Thượng"</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Bạn nắm lấy Terminal và thấy một gương mặt quen thuộc đến phiền phức hiện lên màn hình…</t>
+          <t>Cậu cầm lấy Thiết bị đầu cuối và thấy một gương mặt quen đến phát ngán hiện lên màn hình…</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhà hát 3 "Psyche Pass: The Outlier" - Mở khóa Kết thúc Hai: "The Eternal Watch"</t>
+          <t>Hoàn thành Nhà hát 3 "Psyche Pass: Kẻ Bất Quy Tắc" - Mở khóa Kết thúc 2: "Người Canh Gác Vĩnh Hằng"</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Mortefi đã gia nhập đội của bạn</t>
+          <t>Mortefi đã gia nhập đội của cậu</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Xiangli Yao đã gia nhập đội của bạn</t>
+          <t>Xiangli Yao đã gia nhập đội của cậu</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>"Cái mà bạn gọi là cảnh tượng có thể là {Male=cơn ác mộng;Female=cơn ác mộng} tồi tệ nhất của anh/cô ấy…"</t>
+          <t>"Cái mà cậu gọi là cảnh đẹp có thể lại là cơn ác mộng tồi tệ nhất của {Male=his;Female=her}…"</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3251,8 +3251,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>"Vị khách từ phương xa—"
-"Ngày mai, anh sẽ ra khơi—"</t>
+          <t>"Vị khách phương xa—"
+"Ngày mai ngươi sẽ ra khơi—"</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3323,8 +3323,8 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>"Đi đi, đi ngay bây giờ—"
-"Như vậy là tốt nhất—"</t>
+          <t>"Đi đi, đi ngay đi—"
+"Thế này là tốt nhất rồi—"</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3395,8 +3395,8 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>"Hãy mang theo bài hát này—"
-"Và để lại nụ cười của anh cho tôi—"</t>
+          <t>"Hãy mang bài hát này theo bên mình—"
+"Và để lại nụ cười ấy cho ta—"</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhà hát 4: "Ragunna's Visitor" - Mở khóa Kết thúc Một: "Debts Paid In Full"</t>
+          <t>Hoàn thành Nhà hát 4: "Vị Khách Của Ragunna" - Mở khóa Kết thúc 1: "Món Nợ Đã Đền"</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhà hát 4: "Ragunna's Visitor" - Mở khóa Kết thúc Hai: "The High Adjudicator"</t>
+          <t>Hoàn thành Nhà hát 4: "Vị Khách Của Ragunna" - Mở khóa Kết thúc 2: "Thẩm Phán Tối Cao"</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>"Vị khách từ phương xa—"</t>
+          <t>"Vị khách phương xa—"</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>"Hãy mang theo bài hát này—"</t>
+          <t>"Hãy mang bài hát này theo bên mình—"</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>"Và để lại nụ cười của anh cho tôi—"</t>
+          <t>"Và hãy để lại nụ cười ấy cho ta—"</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ciaccona đã gia nhập đội của bạn</t>
+          <t>Ciaccona đã gia nhập đội của cậu</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Cantarella đã gia nhập đội của bạn</t>
+          <t>Cantarella đã gia nhập đội của ngươi</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>"Ôi không, chúng ta cần phải nhanh lên—"</t>
+          <t>"Ôi không, phải nhanh lên thôi—"</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Đúng, kẻ sát nhân đã giết bốn thành viên thủy thủ đoàn là—</t>
+          <t>Đúng, kẻ giết bốn thành viên thủy thủ đoàn là—</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>"Đợi đã, tôi vẫn còn câu hỏi—"</t>
+          <t>"Đợi đã, tôi vẫn còn thắc mắc—"</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>"Vinh quang, vinh quang, Imperator—"</t>
+          <t>"Vinh quang, vinh quang, Hoàng đế—"</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Dòng chú thích bên dưới viết:</t>
+          <t>Dưới đó có dòng chú thích:</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Cuộc sống có vẻ đẹp của nó;</t>
+          <t>Cuộc sống luôn tiềm ẩn những điều đẹp đẽ;</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Dù nó không thuộc về ta;</t>
+          <t>Dù nó không thuộc về chúng ta;</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Sẽ có người hưởng phần đẹp đẽ ấy;</t>
+          <t>Sẽ có người lấy phần công bằng của mình;</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>"Ring—”</t>
+          <t>"Chuông—"</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>"Ring—”</t>
+          <t>"Chuông—"</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>"Ring—”</t>
+          <t>"Chuông—"</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>"Ring—”</t>
+          <t>"Chuông—"</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Event Bonus</t>
+          <t>Thưởng sự kiện</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Phần thưởng Sự kiện</t>
+          <t>Phần Thưởng Sự Kiện</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Sự kiện đã hoàn thành</t>
+          <t>Hoàn thành - Sự Kiện</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Scene Bonus (Activated)</t>
+          <t>Thưởng Cảnh (Đã kích hoạt)</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Invisible Clench</t>
+          <t>Nắm đấm vô hình</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>True Martial Arts</t>
+          <t>Võ Thuật Chính Thống</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Cái kết của câu chuyện cổ tích</t>
+          <t>Hồi Kết Của Truyện Cổ Tích</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Give Me Wings</t>
+          <t>Ban cho ta đôi cánh</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Stronghold</t>
+          <t>Pháo Đài</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>"Solaris Best Duo"</t>
+          <t>"Bộ đôi xuất sắc nhất Solaris"</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Field Medic</t>
+          <t>Hộ Sĩ Chiến Trường</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Ordinary Commuter</t>
+          <t>Hành Khách Bình Thường</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Công dân gương mẫu</t>
+          <t>Công Dân Mẫu Mực</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Du khách đến Ultrazone</t>
+          <t>Những Vị Khách Đến Vùng Ultrazone</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Psyche Pass</t>
+          <t>Thẻ Tâm Lý</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Kẻ phản nghịch của Mercury Palace</t>
+          <t>Kẻ Nổi Loạn Cung Thủy Ngân</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Dreamscape Requiem</t>
+          <t>Khúc Bi Ca Mộng Ảo</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Bond Overview</t>
+          <t>Tổng Quan Mối Liên Kết</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Area Occupied</t>
+          <t>Khu vực bị chiếm giữ</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp đội</t>
+          <t>Nâng Cấp Đội</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Spectro</t>
+          <t>Vé Mời: Spectro</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Havoc</t>
+          <t>Vé Mời: Havoc</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Fusion</t>
+          <t>Vé Mời: Fusion</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Glacio</t>
+          <t>Vé Mời: Glacio</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Electro</t>
+          <t>Vé Mời: Electro</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Aero</t>
+          <t>Vé Mời: Aero</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Special</t>
+          <t>Vé Mời: Đặc Biệt</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Film Roll</t>
+          <t>Cuộn phim</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Cấp đội</t>
+          <t>Cấp Đội</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Film Roll</t>
+          <t>Cuộn phim</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Cấp đội</t>
+          <t>Cấp Đội</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Đã nhận</t>
+          <t>Nhận được</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Chưa Nhận Được</t>
+          <t>Chưa nhận được</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Resonator Info</t>
+          <t>Thông Tin Resonator</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Illusive Echo</t>
+          <t>Tiếng Vọng Ảo Ảnh</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>Mã Đổi</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Chi tiết Resonator</t>
+          <t>Thông Tin Resonator</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Phần thưởng cấp độ</t>
+          <t>Thưởng Cấp độ</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Mối Liên Kết</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Cửa hàng Chiêu mộ</t>
+          <t>Cửa hàng chiêu mộ</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Film Roll Cost</t>
+          <t>Chi phí Cuộn phim</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Kết thúc và hoàn tất</t>
+          <t>Kết thúc và Xác nhận</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Lưu và Thoát</t>
+          <t>Lưu và thoát</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Energy Regen</t>
+          <t>Hồi Năng Lượng</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Max Film Roll+</t>
+          <t>Đã đạt giới hạn cuộn phim+</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Vision Range+</t>
+          <t>Tầm Nhìn+</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Dream Fragments Gain+</t>
+          <t>Tăng Mảnh Giấc Mơ+</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Film Roll Cost-</t>
+          <t>Chi phí Cuộn phim-</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Không Activated Bond</t>
+          <t>Không có Liên Kết Kích Hoạt</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Điểm Hiện Tại</t>
+          <t>Điểm hiện tại</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Exploration Progress</t>
+          <t>Tiến Độ Thám Hiểm</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Đội Leveling</t>
+          <t>Đang Nâng Cấp Đội</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>"Nhân danh những Anh hùng"</t>
+          <t>"Nhân Danh Những Anh Hùng"</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>"Serenity”</t>
+          <t>"Bình Yên"</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>"Turmoil"</t>
+          <t>"Hỗn Loạn"</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>"Bờ biển Bí ẩn"</t>
+          <t>"Bờ Biển Đầy Bí Ẩn"</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>"The Eternal Watch"</t>
+          <t>"Linh Mục Vĩnh Hằng"</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>"Linh hồn bên kia Hố đen"</t>
+          <t>"Những Linh Hồn Vượt Qua Hố Đen"</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>"Debts Paid In Full"</t>
+          <t>"Món Nợ Đã Được Thanh Toán"</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>"High Adjudicator"</t>
+          <t>"Thẩm Phán Tối Cao"</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>"The Slumbering Seabed"</t>
+          <t>"Vùng Đáy Biển Ngủ Quên"</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>"The Somnoire Breeze"</t>
+          <t>"Làn Gió Ngủ Mơ"</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>"Cái nôi Vĩnh hằng"</t>
+          <t>"Cái Nôi Vĩnh Hằng"</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>"The Long Featurette"</t>
+          <t>"Phim Tài Liệu Dài"</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Connection Lost</t>
+          <t>Mất kết nối</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Danh sách Theo dõi</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>"Tradable Dreams"</t>
+          <t>"Những Giấc Mơ Có Thể Giao Dịch"</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Khúc bi ca từ Mây</t>
+          <t>Khúc Bi Ca Mây Trời</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Echoes of Kiếm Storms</t>
+          <t>Tiếng Vọng Bão Kiếm</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>March of Brutal Packs</t>
+          <t>Hành quân của Bầy Thú Dữ</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Reprise of Overlord Trio</t>
+          <t>Tái Ngộ Tam Hùng Bá Chủ</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Data Overflow</t>
+          <t>Dữ liệu Tràn Bộ Nhớ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Bugged Conditions</t>
+          <t>Điều Kiện Bất Thường</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Applause for the Swift</t>
+          <t>Tiếng Vỗ Tay Cho Kẻ Nhanh Nhẹn</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Mimic Siege</t>
+          <t>Bao Vây Quái Giả Hình</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Discord Surge</t>
+          <t>Sóng Tacet Discord Trỗi Dậy</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Arena Anomaly</t>
+          <t>Dị Thường Đấu Trường</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Snowball Effect</t>
+          <t>Hiệu Ứng Bóng Tuyết</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>The Three Knights</t>
+          <t>Ba Hiệp Sĩ</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng</t>
+          <t>Skill Level</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Maxed Out</t>
+          <t>Đã đạt tối đa</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Recruit Ticket: Flame Ranger</t>
+          <t>Vé Mời: Flame Ranger</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng có Chixia</t>
+          <t>Mở Cửa Hàng Tuyển Mộ có Chixia</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Random Resonator</t>
+          <t>Resonator Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Tuyển Dụng một Resonator Ngẫu Nhiên</t>
+          <t>Mời ngẫu nhiên một Resonator</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Thử Thách Cuối</t>
+          <t>Thử Thách Cuối Cùng</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Main Story</t>
+          <t>Câu Chuyện Chính</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Boss Battle</t>
+          <t>Trận Chiến Trùm</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Common Battle</t>
+          <t>Trận Chiến Thường</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Elite Battle</t>
+          <t>Đấu Trường Tinh Anh</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Random Event</t>
+          <t>Sự Kiện Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Recruitment Event</t>
+          <t>Sự kiện chiêu mộ</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Respite Event</t>
+          <t>Sự Kiện Nghỉ Dưỡng</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Battle Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cao Nguyên</t>
+          <t>Giấc Mộng Cao Nguyên</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Tranquil Heart</t>
+          <t>Tâm An</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Brilliant Tacetite Bloom</t>
+          <t>Đóa Tacetite Rực Rỡ</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Hazardous Data</t>
+          <t>Dữ liệu Nguy hiểm</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Blistering Gemstone</t>
+          <t>Đá Quý Rực Lửa</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Vibrant Lightning</t>
+          <t>Tia Chớp Sôi Động</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Wonderland Phantasm</t>
+          <t>Ảo Ảnh Kỳ Diệu</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Blue Night Waltz</t>
+          <t>Điệu Van-xơ Đêm Xanh</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Dusty Book</t>
+          <t>Quyển Sách Bám Bụi</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Unordered Cube</t>
+          <t>Khối Lập Phương Lộn Xộn</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Electric Wings</t>
+          <t>Đôi Cánh Điện</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Protective Gauntlets</t>
+          <t>Găng Tay Bảo Hộ</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Old Revolver</t>
+          <t>Khẩu Súng Lục Cũ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Swift Sabre</t>
+          <t>Kiếm Nhanh</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Supergravity Hammer</t>
+          <t>Búa Siêu Trọng Lực</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Supercharged Gauntlets</t>
+          <t>Găng Tay Siêu Tải</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Soothing Aromatherapy</t>
+          <t>Liệu Pháp Thư Giãn</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Blood Debt</t>
+          <t>Món nợ máu</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Prostheic Razor</t>
+          <t>Lưỡi Dao Giả</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Cardiotonic</t>
+          <t>Thuốc Tăng Cường Tim</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Ultra I</t>
+          <t>Feilian Beringal - Siêu Cấp I</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Ảo Tưởng Vô Hồi - Ultra I</t>
+          <t>Ảo Tưởng Vô Hồi - Cực I</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Feeble I</t>
+          <t>Kẻ yếu đuối I</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Healing Prevention I</t>
+          <t>Ngăn hồi phục I</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Delayed Effect I</t>
+          <t>Hiệu ứng trì hoãn I</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Obstinance I</t>
+          <t>Cố Chấp I</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Toughness I</t>
+          <t>Sức chịu đựng I</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Dirge Sonata</t>
+          <t>Khúc Bi Ca Tang Lễ</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Rust Mirage</t>
+          <t>Ảo Ảnh Gỉ Sét</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Healing Mirage</t>
+          <t>Ảo ảnh hồi phục</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Volatile Mirage</t>
+          <t>Ảo Ảnh Bất Định</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Feeble Mirage</t>
+          <t>Ảo ảnh mỏng manh</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Burstpoint</t>
+          <t>Điểm Bùng Nổ</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Strike Mirage</t>
+          <t>Đòn đánh ảo ảnh!</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Shield Mirage</t>
+          <t>Khiên Ảo Ảnh</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Surge Mirage</t>
+          <t>Ảo Ảnh Dòng Năng Lượng</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Swift Recoil</t>
+          <t>Phản Đòn Nhanh</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Sluggish</t>
+          <t>Uể oải</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Dirge Staccato: Rage</t>
+          <t>Đoạn Bi Ca Ngắn: Thịnh Nộ</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Dirge Staccato: Cure</t>
+          <t>Đoạn Bi Ca Ngắn: Hồi Phục</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Berserk</t>
+          <t>Cuồng Nộ</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Dramatic Echoes</t>
+          <t>Tiếng Vọng Kịch Tính</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tempering</t>
+          <t>Đang tôi luyện</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Falling Blade</t>
+          <t>Lưỡi Kiếm Sa Ngã</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Thunder of Bane</t>
+          <t>Sấm Sét Tận Thế</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Screech</t>
+          <t>Tiếng Rít</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Cacophony</t>
+          <t>Hỗn Âm</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Brittle</t>
+          <t>Giòn vỡ</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Resilient Blade</t>
+          <t>Lưỡi Kiếm Kiên Cường</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Pháo Đài Tuyệt Vọng: Giáo</t>
+          <t>Pháo Đài Tuyệt Vọng: Thương</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Shatter Impact</t>
+          <t>Tác Động Phá Hủy</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17120,7 +17120,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Rage March</t>
+          <t>Hành Quân Thịnh Nộ</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Shock Stump</t>
+          <t>Gốc Sốc Điện</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Healing Stump</t>
+          <t>Gốc cây hồi phục</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Singularity</t>
+          <t>Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Repulsive Force</t>
+          <t>Lực Đẩy</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Rage Leech</t>
+          <t>Hút Máu Thịnh Nộ</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Rage Defense</t>
+          <t>Hộ Thể Thịnh Nộ</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Rage Healing</t>
+          <t>Hồi Phục Thịnh Nộ</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Frenzy Swarm</t>
+          <t>Bầy Cuồng Nộ</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Tough Swarm</t>
+          <t>Bầy Đàn Khắc Nghiệt</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Static Effect</t>
+          <t>Hiệu Ứng Tĩnh</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Iron Resolve</t>
+          <t>Ý Chí Thép</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Overlord Reprise</t>
+          <t>Khúc Tái Diễn Chúa Tể</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Trill Frostbite</t>
+          <t>Rét cắt da cắt thịt...</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Marcato Frostbite</t>
+          <t>Marcato - Băng Giá</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Burning Heart</t>
+          <t>Trái Tim Rực Lửa</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Windswept Surface</t>
+          <t>Bề Mặt Gió Cuốn</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18380,7 +18380,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Không-Fly Zone</t>
+          <t>Khu vực cấm bay</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Accelerating Raid</t>
+          <t>Đột Kích Tăng Tốc</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Decelerating Burden</t>
+          <t>Gánh Nặng Giảm Tốc</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Deep Backlash</t>
+          <t>Phản Đòn Sâu</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Resistance Matrix</t>
+          <t>Ma Trận Kháng Cự</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18730,7 +18730,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Joint Effort</t>
+          <t>Hợp Tác</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Precise Blow</t>
+          <t>Đòn Chính Xác</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Reconstruction Overload</t>
+          <t>Quá Tải Tái Cấu Trúc</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19010,7 +19010,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Blessing</t>
+          <t>Phước Lành</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Breathing Technique</t>
+          <t>Kỹ Thuật Điều Hô Hấp</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Fleeting Streak</t>
+          <t>Vệt Phù Du</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Fortification</t>
+          <t>Cường hóa</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19360,7 +19360,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Không Chiến Tầm Gần</t>
+          <t>Hỗ trợ không kích gần</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Lead Tempo</t>
+          <t>Nhịp dẫn đầu</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Delayed Burst</t>
+          <t>Vụ nổ trì hoãn</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Fatigue Impact</t>
+          <t>Tác Động Mệt Mỏi</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19640,7 +19640,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Feeble II</t>
+          <t>Kẻ yếu đuối II</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Healing Prevention II</t>
+          <t>Ngăn hồi phục II</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Delayed Effect II</t>
+          <t>Hiệu ứng trì hoãn II</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Obstinance II</t>
+          <t>Cố Chấp II</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Toughness II</t>
+          <t>Sức chịu đựng II</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Ultra II</t>
+          <t>Feilian Beringal - Siêu Cấp II</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ảo Tưởng Vô Hồi - Ultra II</t>
+          <t>Ảo Tưởng Vô Hồi - Cực II</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20410,7 +20410,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Feilian Beringal - Ultra III</t>
+          <t>Feilian Beringal - Siêu Cấp III</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Ảo Tưởng Vô Hồi - Ultra III</t>
+          <t>Ảo Tưởng Vô Hồi - Cực III</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Symphony of Bubbles</t>
+          <t>Giao Hưởng Bong Bóng</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>The Shielded Thorn</t>
+          <t>Gai Khiên</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Symbiotic Horde</t>
+          <t>Bầy Đồng Minh Cộng Sinh</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20760,7 +20760,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Last Cry of Fallacies</t>
+          <t>Tiếng Thét Cuối Cùng của Ảo Tưởng</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Stimulation Tactic</t>
+          <t>Chiến Thuật Kích Thích</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Hoàn thành Khúc Bi Ca Mây Trời với Stress Mô-đun Burstpoint được trang bị</t>
+          <t>Hoàn thành Khúc Bi Ca Mây Trời với Mô-đun Áp Lực: Điểm Bùng Nổ được trang bị</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Hoàn thành Khúc Bi Ca Mây Trời với Stress Mô-đun Berserk được trang bị</t>
+          <t>Hoàn thành Khúc Bi Ca Mây Trời với Mô-đun Áp Lực: Cuồng Chiến được trang bị</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Hoàn thành Echoes of Kiếm Storms với Stress Mô-đun Solo trang bị</t>
+          <t>Hoàn thành Echo Bão Kiếm với Mô-đun Áp Lực: Đơn Độc được trang bị</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Hoàn thành Echoes of Kiếm Storms với Stress Mô-đun Thunder of Bane trang bị</t>
+          <t>Hoàn thành Echo Bão Kiếm với Mô-đun Áp Lực: Sấm Nguyền được trang bị</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21390,7 +21390,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hoàn thành March of Brutal Packs với Stress Mô-đun Repulsive Force trang bị</t>
+          <t>Hoàn thành Hành Quân Bầy Thú Dữ với Mô-đun Căng Thẳng Lực Đẩy</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hoàn thành March of Brutal Packs với Stress Mô-đun Art of Precision trang bị</t>
+          <t>Hoàn thành Hành Quân Bầy Thú Dữ với Mô-đun Căng Thẳng Nghệ Thuật Chính Xác</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hoàn thành Reprise of Overlord Trio với Stress Mô-đun Burning Heart trang bị</t>
+          <t>Hoàn thành Reprise of Overlord Trio với module Stress Burning Heart trang bị</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Hoàn thành Reprise of Overlord Trio với Stress Mô-đun Precise Blow trang bị</t>
+          <t>Hoàn thành "Bản Phối Lại Của Bộ Ba Chúa Tể" với Bộ Căng Thẳng - Đòn Đánh Chính Xác</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Hoàn thành Elegy from the Clouds với Stress Mô-đun Volatile Mirage và Surge Mirage trang bị</t>
+          <t>Hoàn thành "Elegy from the Clouds" với Stress Module Volatile Mirage và Surge Mirage được trang bị</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Hoàn thành Echoes of Kiếm Storms với Stress Mô-đun Tempering và Shatter Impact trang bị</t>
+          <t>Hoàn thành Echo Bão Kiếm với Mô-đun Áp Lực: Tôi Luyện và Va Chạm Vỡ được trang bị</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Hoàn thành March of Brutal Packs với Stress Mô-đun Rage Leech và Rage Healing trang bị</t>
+          <t>Hoàn thành Hành Quân Bầy Thú Dữ với Mô-đun Căng Thẳng Hút Giận và Hồi Phục Giận</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21880,7 +21880,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Hoàn thành March of Brutal Packs với Stress Mô-đun Tough Swarm và Iron Resolve trang bị</t>
+          <t>Hoàn thành Hành Quân Bầy Thú Dữ với Mô-đun Căng Thẳng Bầy Kiên Cường và Ý Chí Sắt Đá</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21950,7 +21950,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Data Overflow ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Tràn Dữ Liệu ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Bugged Conditions ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Điều Kiện Lỗi ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Applause for the Swift ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Tiếng Vỗ Tay Cho Kẻ Nhanh Nhẹn ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Mimic Siege ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Bao Vây Giả ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Tacet Discord Surge ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Bùng Nổ Tacet Discord ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Arena Anomaly ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Dị Thường Đấu Trường ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - Snowball Effect ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Hiệu Ứng Quả Tuyết Lăn ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trial - The Three Nights ở Stress Level 6</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng - Ba Đêm Đen ở Cấp Độ Áp Lực 6</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22510,7 +22510,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 8 trong Disaster Trial</t>
+          <t>Đạt Cấp Độ Căng Thẳng Tổng 8 trong Thử Thách Thiên Tai.</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 16 trong Disaster Trial</t>
+          <t>Đạt Tổng Mức Căng Thẳng 16 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 24 trong Disaster Trial</t>
+          <t>Đạt Tổng Mức Căng Thẳng 24 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 32 trong Disaster Trial</t>
+          <t>Đạt Tổng Mức Căng Thẳng 32 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 40 trong Disaster Trial</t>
+          <t>Đạt Tổng Mức Căng Thẳng 40 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 48 trong Disaster Trial</t>
+          <t>Đạt Tổng Mức Căng Thẳng 48 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Đạt Tổng Stress Level 64 trong Disaster Trial</t>
+          <t>Đạt Cấp Độ Căng Thẳng Tổng 64 trong Thử Thách Thiên Tai.</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 88 trong Thử Thách Tai Họa</t>
+          <t>Đạt Cấp Độ Căng Thẳng Tổng 88 trong Thử Thách Thiên Tai.</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23070,7 +23070,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 104 trong Thử Thách Tai Họa</t>
+          <t>Đạt Tổng Mức Căng Thẳng 104 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 120 trong Thử Thách Tai Họa</t>
+          <t>Đạt Tổng Mức Căng Thẳng 120 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 136 trong Thử Thách Tai Họa</t>
+          <t>Đạt Tổng Mức Căng Thẳng 136 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 140 trong Thử Thách Tai Họa</t>
+          <t>Đạt Tổng Mức Căng Thẳng 140 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 144 trong Thử Thách Tai Họa</t>
+          <t>Đạt Tổng Mức Căng Thẳng 144 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Đạt Tổng Mức Độ Căng Thẳng 148 trong Thử Thách Tai Họa</t>
+          <t>Đạt Tổng Mức Căng Thẳng 148 trong Thử Thách Tai Họa</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23560,7 +23560,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23630,7 +23630,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Đang tải, vui lòng chờ</t>
+          <t>Đang tải, xin chờ</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23770,7 +23770,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Timed Burst</t>
+          <t>Kích Nổ Định Thời</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Binding Traps</t>
+          <t>Bẫy Giam Cầm</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Shield Fight</t>
+          <t>Khiên Chiến Đấu</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Lightning Raid</t>
+          <t>Đột Kích Sấm Sét</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Escalating Battle</t>
+          <t>Trận Chiến Nảy Lửa</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24120,7 +24120,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Hostile Tides</t>
+          <t>Thủy Triều Thù Địch</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24190,7 +24190,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Aerial Strikes</t>
+          <t>Đòn Đánh Trên Không</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Unyielding Foes</t>
+          <t>Kẻ Thù Bất Khuất</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24330,7 +24330,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Virtual Vanquisher</t>
+          <t>Kẻ Tiêu Diệt Ảo</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Bổ Sung Mile I</t>
+          <t>Nỗ Lực Thêm I</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24470,7 +24470,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Bổ Sung Mile II</t>
+          <t>Vượt Trội II</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24540,7 +24540,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Bổ Sung Mile III</t>
+          <t>Vượt Trội III</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Shattered Dreams</t>
+          <t>Giấc Mộng Tan Vỡ</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Hoàn thành "Chạy Thử" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Chạy Thử" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Hoàn thành "Thiên Đàng Bậc Thang" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Thiên Đàng Bậc Thang" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Hoàn thành "Thác Nước Xoáy" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Dòng Nước Xoáy" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Hoàn thành "Phố Mua Bán" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Phố Đổi Chác" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25030,7 +25030,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Hoàn thành "Buổi Biểu Diễn Không Kịch Bản" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Scriptless Show" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Hoàn thành "Đêm Hy Sinh" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Sacrifice Night" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25240,7 +25240,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Hoàn thành "Mê Cung Gương" ở bất kỳ độ khó nào</t>
+          <t>Hoàn thành "Mirror Maze" ở bất kỳ độ khó nào.</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Quản lý Dreamland trong 30 ngày trong một lượt chơi</t>
+          <t>Quản lý Dreamland trong 30 ngày liên tục</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Quản lý Dreamland trong 35 ngày trong một lượt chơi</t>
+          <t>Quản lý Dreamland trong 35 ngày liên tục</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25450,7 +25450,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Quản lý Dreamland trong 40 ngày trong một lượt chơi</t>
+          <t>Quản lý Dreamland trong 40 ngày liên tục</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25590,7 +25590,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Tốt nghiệp tổng cộng 10 lần</t>
+          <t>Tiến Hóa 10 lần liên tiếp</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25660,7 +25660,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Trao đổi tổng cộng 10 lần</t>
+          <t>Đổi tổng cộng 10 lần</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào với Dream of Gradation</t>
+          <t>Hoàn thành bất kỳ cấp độ nào của Dream of Gradation.</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào với Dream of Devouring</t>
+          <t>Hoàn thành bất kỳ cấp độ nào của Dream of Devouring.</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào với Dream of Exchange</t>
+          <t>Hoàn thành bất kỳ cấp độ nào của Dream of Exchange.</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Hoàn thành bất kỳ độ khó nào với Dream of Integration</t>
+          <t>Hoàn thành bất kỳ cấp độ nào của Dream of Integration.</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Hoàn thành 5 độ khó với Dream of Gradation</t>
+          <t>Hoàn thành 5 độ khó trong Dream of Gradation.</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Hoàn thành 5 độ khó với Dream of Devouring</t>
+          <t>Hoàn thành 5 độ khó trong Dream of Devouring.</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26220,7 +26220,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Hoàn thành 5 độ khó với Dream of Exchange</t>
+          <t>Hoàn thành 5 độ khó trong Dream of Exchange.</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Hoàn thành 5 độ khó với Dream of Integration</t>
+          <t>Hoàn thành 5 độ khó trong Dream of Integration.</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Mở Khóa 30 Thành Viên Dreamland</t>
+          <t>Mở khóa 30 Thành Viên Dreamland</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Mở Khóa 50 Thành Viên Dreamland</t>
+          <t>Mở khóa 50 Thành viên Dreamland</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26500,7 +26500,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Mở khóa tất cả Dreamland Members</t>
+          <t>Mở khóa tất cả Thành viên Dreamland.</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26570,7 +26570,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Mở Khóa 30 Đạo Cụ Dreamland</t>
+          <t>Mở khóa 30 Đạo Cụ Dreamland</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Mở Khóa 35 Đạo Cụ Dreamland</t>
+          <t>Mở khóa 35 Đạo Cụ Dreamland</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26710,7 +26710,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Mở Khóa 40 Đạo Cụ Dreamland</t>
+          <t>Mở khóa 40 Đạo Cụ Dreamland</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Sử dụng bất kỳ Phantasma Blessing 1 lần</t>
+          <t>Sử dụng Phantasma Blessing một lần</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Sử dụng bất kỳ Phantasma Blessing 5 lần</t>
+          <t>Sử dụng Phước Lành Ảo Ảnh 5 lần</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26920,7 +26920,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 40.000 Dreamland Coupons</t>
+          <t>Thu thập tổng cộng 40.000 Phiếu Mộng Ảo.</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 80.000 Dreamland Coupons</t>
+          <t>Thu thập tổng cộng 80.000 Phiếu Dreamland</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 150.000 Dreamland Coupons</t>
+          <t>Thu thập tổng cộng 150.000 Phiếu Dreamland</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 50 Frequency Crystals</t>
+          <t>Thu thập tổng cộng 50 Tinh Thể Tần Số</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 100 Frequency Crystals</t>
+          <t>Thu thập tổng cộng 100 Tinh Thể Tần Số</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27270,7 +27270,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Mở khóa Dream Boon: Shop Bonus</t>
+          <t>Mở Đặc Ân Giấc Mơ: Ưu Đãi Cửa Hàng</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Mở khóa Dream Boon: Precious Item II</t>
+          <t>Mở Đặc Ân Giấc Mơ: Vật Phẩm Quý II</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Mở khóa Dream Boon: More the Merrier II</t>
+          <t>Mở Đặc Ân Giấc Mơ: Đông Vui Hơn II</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Mua 10 lần trong Dreamland Shop</t>
+          <t>Mua 10 lần tại Cửa Hàng Xứ Mộng</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27550,7 +27550,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Mua 20 lần trong Dreamland Shop</t>
+          <t>Mua 20 lần tại Cửa Hàng Xứ Mộng</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>First Night Gift</t>
+          <t>Món quà đêm đầu</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Starting Funds I</t>
+          <t>Quỹ Khởi Đầu I</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27760,7 +27760,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Quality Boost</t>
+          <t>Tăng Cường Chất Lượng</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Shop Bonus</t>
+          <t>Ưu Đãi Cửa Hàng</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27900,7 +27900,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Shop Revamp</t>
+          <t>Cửa Hàng Đổi Mới</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27970,7 +27970,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Paradise Overhaul</t>
+          <t>Thiên Đường Đổi Mới</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Vật Phẩm Quý Giá I</t>
+          <t>Vật phẩm quý giá I</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Quality Sales I</t>
+          <t>Đợt Giảm Giá Chất Lượng I</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28180,7 +28180,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Prop Capacity I</t>
+          <t>Sức chứa vật phẩm I</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28250,7 +28250,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Càng Đông Càng Vui I</t>
+          <t>Càng đông càng vui I</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28320,7 +28320,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>First Steps</t>
+          <t>Bước Đi Đầu Tiên</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28390,7 +28390,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Starting Funds II</t>
+          <t>Quỹ Khởi Đầu II</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Vật Phẩm Quý Giá II</t>
+          <t>Vật phẩm quý giá II</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Quality Sales II</t>
+          <t>Đợt Giảm Giá Chất Lượng II</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28600,7 +28600,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Dreamland Detail</t>
+          <t>Chi Tiết Giấc Mơ</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Sản Lượng Hôm Nay</t>
+          <t>Sản lượng hôm nay</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28740,7 +28740,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Desolate ruins, roaming Echoes, đây là thiên đường hậu nhân loại—</t>
+          <t>Tàn tích hoang vu, những Echo lang thang—đây là thiên đường hậu nhân loại...</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Echoes giờ đây sinh sôi nơi con người từng sống…</t>
+          <t>Nơi con người từng sống giờ đây chỉ còn Echo ngân vang…</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28880,7 +28880,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Nếu vậy, hãy để ta chứng kiến nơi bản giao hưởng cuối cùng này sẽ an nghỉ…</t>
+          <t>Nếu vậy, hãy để ta chứng kiến nơi bản giao hưởng cuối cùng này sẽ đổ dồn về đâu…</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tiếp Theo</t>
+          <t>Tiếp theo</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Xác Nhận</t>
+          <t>Xác nhận</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Cửa Hàng Dreamland</t>
+          <t>Cửa Hàng Giấc Mơ</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Ẩn giao diện này</t>
+          <t>Ẩn giao diện này đi</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29510,7 +29510,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Infinite Mode</t>
+          <t>Chế Độ Vô Tận</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29720,7 +29720,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29790,7 +29790,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>New Record</t>
+          <t>Kỷ Lục Mới</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Nâng cấp Successful</t>
+          <t>Nâng Cấp Thành Công</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29930,7 +29930,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Chạm vào bất kỳ đâu để đóng</t>
+          <t>Nhấn bất kỳ đâu để đóng</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30140,7 +30140,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Mục tiêu Giai đoạn</t>
+          <t>Mục Tiêu Giai Đoạn</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30210,7 +30210,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Phần Thưởng</t>
+          <t>Phần thưởng</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Hoàn thành lần đầu</t>
+          <t>Hoàn Thành Lần Đầu</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30420,7 +30420,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Môi trường giai đoạn</t>
+          <t>Môi Trường Giai Đoạn</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30490,7 +30490,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Prop Capacity II</t>
+          <t>Sức chứa vật phẩm II</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30560,7 +30560,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Càng Đông Càng Vui II</t>
+          <t>Càng đông càng vui II</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Sử Dụng Phước Lành</t>
+          <t>Sử dụng Phước Lành</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30700,7 +30700,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Blessings Used Up</t>
+          <t>Đã Hết Phúc Lành</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Dream Block: Watermirror</t>
+          <t>Khối Mộng: Gương Nước</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30910,7 +30910,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Dream Block: Obsidian</t>
+          <t>Khối Mộng: Hắc Diện Thạch</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Dream Block: Gravel</t>
+          <t>Khối Mộng: Sỏi Đá</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31050,7 +31050,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Dream Block: Ice Shards</t>
+          <t>Khối Mộng: Mảnh Băng</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31120,7 +31120,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Dream Block: Woodland</t>
+          <t>Khối Mộng: Rừng Cũ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31190,7 +31190,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Dream Block: Forbidden</t>
+          <t>Khối Mộng: Cấm Địa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31260,7 +31260,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Dream Block: Blackstone</t>
+          <t>Khối Giấc Mơ: Blackstone</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Highest Dreamland Coupons</t>
+          <t>Phiếu Giấc Mơ Cao Nhất</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31470,7 +31470,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>New Dream Boon</t>
+          <t>Ước Nguyện Mộng Mới</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Chưa có thành quả</t>
+          <t>Vẫn chưa đầu hàng</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31750,7 +31750,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Tycoon's Street</t>
+          <t>Phố Tài Phiệt</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31820,7 +31820,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Welcome Resort</t>
+          <t>Khu Nghỉ Dưỡng Welcome</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31890,7 +31890,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Brainpower Room</t>
+          <t>Phòng Suy Nghĩ</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31960,7 +31960,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Oven Restaurant</t>
+          <t>Nhà hàng Lò Nướng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32030,7 +32030,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Big Haul Dock</t>
+          <t>Bến Cảng Lớn</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Carnival Fountain</t>
+          <t>Đài Phun Nước Lễ Hội</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32170,7 +32170,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>A-okay Harbor</t>
+          <t>Bến Cảng A-okay</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32240,7 +32240,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Scenario 1</t>
+          <t>Kịch Bản 1</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32310,7 +32310,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Scenario 2</t>
+          <t>Kịch Bản 2</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Scenario 3</t>
+          <t>Kịch Bản 3</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Scenario 4</t>
+          <t>Kịch Bản 4</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32520,7 +32520,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Scenario 5</t>
+          <t>Chương 5</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32590,7 +32590,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Scenario 6</t>
+          <t>Chương 6</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32660,7 +32660,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Scenario 7</t>
+          <t>Chương 7</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32730,7 +32730,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Top Hat Trader</t>
+          <t>Thương Nhân Mũ Cao Bồi</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32800,7 +32800,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Một Bông Hoa Nhỏ Dành Cho Bạn</t>
+          <t>Một Bông Hoa Nhỏ Dành Cho Cậu</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Anonymous Designer</t>
+          <t>Nhà thiết kế ẩn danh</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Casual Beta Tester</t>
+          <t>Người Thử Nghiệm Beta Thường</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33010,7 +33010,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Nameless Beta Tester</t>
+          <t>Người Thử Nghiệm Beta Vô Danh</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Housekeeping Master</t>
+          <t>Bậc Thầy Quản Gia</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33150,7 +33150,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Plant Caretaker</t>
+          <t>Người Chăm Sóc Thực Vật</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33290,7 +33290,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Chủ Nhân Đuôi Xù</t>
+          <t>Chủ Nhân Đuôi Bông Xù</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33360,7 +33360,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Deadline Survivor</t>
+          <t>Kẻ Sống Sót Cuối Cùng</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33430,7 +33430,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Echo Lover P</t>
+          <t>Người Yêu Tiếng Vọng P</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33500,7 +33500,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Angler Who Never Misses</t>
+          <t>Ngư Phu Bách Phát Bách Trúng</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33570,7 +33570,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Almighty Info Broker A</t>
+          <t>Người môi giới Thông tin Toàn năng A</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33640,7 +33640,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Mười Năm Rèn Luyện Trên Núi</t>
+          <t>Mười Năm Tu Luyện Trên Núi</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Echo Lover P</t>
+          <t>Người Yêu Tiếng Vọng P</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33780,7 +33780,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Strategy Group Beta Tester</t>
+          <t>Thử nghiệm viên Nhóm Chiến lược Beta</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33850,7 +33850,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Happy Beta Tester</t>
+          <t>Người Thử Nghiệm Beta Hạnh Phúc</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Gladiator Training Buy 10 Get 1 Free</t>
+          <t>Huấn Luyện Đấu Sĩ - Mua 10 Tặng 1</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Fluffy Squishy Kitty</t>
+          <t>Mèo bông mềm nhũn</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34060,7 +34060,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Late-Night Gourmet</t>
+          <t>Gourmet Đêm Khuya</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34130,7 +34130,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Vẻ mặt cậu ấy hơi kỳ quặc…</t>
+          <t>Vẻ mặt hắn có gì đó kỳ lạ…</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34270,7 +34270,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Sales Champ</t>
+          <t>Quán Quân Bán Hàng</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Bowtie Butler</t>
+          <t>Quản Gia Nơ Bướm</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Transport Namipon</t>
+          <t>Vận Chuyển Namipon</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34550,7 +34550,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Sweet Tooth Namipon</t>
+          <t>Namipon Háu Ăn Ngọt</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Rapper Namipon</t>
+          <t>Namipon Rapper</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34760,7 +34760,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Vacationer Namipon</t>
+          <t>Du khách Namipon</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Adventurer Namipon</t>
+          <t>Nhóc Phiêu Lưu Namipon</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34970,7 +34970,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Học Sinh Namipon</t>
+          <t>Học sinh Namipon</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Traveler Namipon</t>
+          <t>Lữ Khách Namipon</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35250,7 +35250,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Jobless Namipon</t>
+          <t>Namipon Thất Nghiệp</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Ninja Namipon</t>
+          <t>Namipon Ninja</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35390,7 +35390,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sakura Quarter</t>
+          <t>Khu Sakura</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35460,7 +35460,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Sakura Quarter</t>
+          <t>Khu Sakura</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35530,7 +35530,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Meishin Passageway</t>
+          <t>Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
